--- a/data/nzd0165/nzd0165.xlsx
+++ b/data/nzd0165/nzd0165.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H386"/>
+  <dimension ref="A1:H389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12018,6 +12018,96 @@
         <v>412.37</v>
       </c>
       <c r="H386" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>434.55</v>
+      </c>
+      <c r="C387" t="n">
+        <v>410.83</v>
+      </c>
+      <c r="D387" t="n">
+        <v>411.09</v>
+      </c>
+      <c r="E387" t="n">
+        <v>404.96</v>
+      </c>
+      <c r="F387" t="n">
+        <v>400.98</v>
+      </c>
+      <c r="G387" t="n">
+        <v>411.1</v>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>432.77</v>
+      </c>
+      <c r="C388" t="n">
+        <v>411.77</v>
+      </c>
+      <c r="D388" t="n">
+        <v>410.57</v>
+      </c>
+      <c r="E388" t="n">
+        <v>403.93</v>
+      </c>
+      <c r="F388" t="n">
+        <v>400.65</v>
+      </c>
+      <c r="G388" t="n">
+        <v>410.68</v>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>432.77</v>
+      </c>
+      <c r="C389" t="n">
+        <v>411.46</v>
+      </c>
+      <c r="D389" t="n">
+        <v>410.43</v>
+      </c>
+      <c r="E389" t="n">
+        <v>403.94</v>
+      </c>
+      <c r="F389" t="n">
+        <v>400.32</v>
+      </c>
+      <c r="G389" t="n">
+        <v>410.52</v>
+      </c>
+      <c r="H389" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12034,7 +12124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B411"/>
+  <dimension ref="A1:B414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16147,6 +16237,36 @@
       </c>
       <c r="B411" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>
@@ -16315,28 +16435,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1010291594402945</v>
+        <v>0.1067884324969807</v>
       </c>
       <c r="J2" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K2" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01848970898936575</v>
+        <v>0.02088288687556905</v>
       </c>
       <c r="M2" t="n">
-        <v>4.24953849519237</v>
+        <v>4.246386726617079</v>
       </c>
       <c r="N2" t="n">
-        <v>29.19113931842811</v>
+        <v>29.07572662194866</v>
       </c>
       <c r="O2" t="n">
-        <v>5.402882500890438</v>
+        <v>5.392191263479873</v>
       </c>
       <c r="P2" t="n">
-        <v>426.9409671489501</v>
+        <v>426.8787097997621</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16393,28 +16513,28 @@
         <v>0.0638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0208916685416095</v>
+        <v>0.02693066646600724</v>
       </c>
       <c r="J3" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K3" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001071557375800003</v>
+        <v>0.001800308015044494</v>
       </c>
       <c r="M3" t="n">
-        <v>3.848573638329089</v>
+        <v>3.845584353308507</v>
       </c>
       <c r="N3" t="n">
-        <v>21.9208801408963</v>
+        <v>21.86768790293913</v>
       </c>
       <c r="O3" t="n">
-        <v>4.681973957733672</v>
+        <v>4.676289972076061</v>
       </c>
       <c r="P3" t="n">
-        <v>406.8863379476081</v>
+        <v>406.8210400004351</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16471,28 +16591,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01915986056721806</v>
+        <v>0.02436546719996021</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K4" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001257554038434194</v>
+        <v>0.002055722919553804</v>
       </c>
       <c r="M4" t="n">
-        <v>3.225499935155089</v>
+        <v>3.221067048896789</v>
       </c>
       <c r="N4" t="n">
-        <v>15.70740075697212</v>
+        <v>15.67217413574094</v>
       </c>
       <c r="O4" t="n">
-        <v>3.963256332483696</v>
+        <v>3.958809686729199</v>
       </c>
       <c r="P4" t="n">
-        <v>406.8155837804134</v>
+        <v>406.7593051664946</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16549,28 +16669,28 @@
         <v>0.0835</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.006635842977517669</v>
+        <v>-0.007292563197062764</v>
       </c>
       <c r="J5" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000147453588805857</v>
+        <v>0.0001811087790755117</v>
       </c>
       <c r="M5" t="n">
-        <v>3.121356956575585</v>
+        <v>3.102014853436293</v>
       </c>
       <c r="N5" t="n">
-        <v>16.08664938259188</v>
+        <v>15.96541773204402</v>
       </c>
       <c r="O5" t="n">
-        <v>4.010816548109859</v>
+        <v>3.995674878170647</v>
       </c>
       <c r="P5" t="n">
-        <v>404.8777035177562</v>
+        <v>404.8848110702317</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16627,28 +16747,28 @@
         <v>0.0956</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09525016542936941</v>
+        <v>-0.09743074638969809</v>
       </c>
       <c r="J6" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K6" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02751567983102632</v>
+        <v>0.02920835072432704</v>
       </c>
       <c r="M6" t="n">
-        <v>3.186239435757566</v>
+        <v>3.174444141687404</v>
       </c>
       <c r="N6" t="n">
-        <v>17.2753407400047</v>
+        <v>17.15730628462453</v>
       </c>
       <c r="O6" t="n">
-        <v>4.156361478505533</v>
+        <v>4.14213788817134</v>
       </c>
       <c r="P6" t="n">
-        <v>404.6038566791121</v>
+        <v>404.6274383398347</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16705,28 +16825,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1019599706554876</v>
+        <v>-0.1019312985922358</v>
       </c>
       <c r="J7" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K7" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03182817815402283</v>
+        <v>0.03234015978468707</v>
       </c>
       <c r="M7" t="n">
-        <v>3.404244201265403</v>
+        <v>3.379593331039628</v>
       </c>
       <c r="N7" t="n">
-        <v>17.03698913747637</v>
+        <v>16.90572181013353</v>
       </c>
       <c r="O7" t="n">
-        <v>4.127588780084126</v>
+        <v>4.111656820569237</v>
       </c>
       <c r="P7" t="n">
-        <v>413.4675356882435</v>
+        <v>413.4672299372172</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16764,7 +16884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H386"/>
+  <dimension ref="A1:H389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32979,6 +33099,132 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>-36.764376886333125,175.1446583488711</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>-36.76461620391964,175.14542600523737</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-36.764439357257,175.14614316352672</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-36.76418117036359,175.14688570847196</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>-36.76381310217629,175.14760813724507</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>-36.76330194493537,175.148232560043</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>-36.7643929240769,175.14465809165196</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>-36.764607831950656,175.14542440760215</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-36.76444365137108,175.14614549381488</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-36.76418896401173,175.146891972066</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>-36.76381545125245,175.14761040318027</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>-36.76330487700733,175.14823553398543</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>-36.7643929240769,175.14465809165196</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>-36.76461059291915,175.1454249344818</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-36.76444480747871,175.14614612120022</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-36.76418888834524,175.1468919112544</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>-36.763817800328546,175.1476126691156</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>-36.76330599398711,175.14823666691592</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0165/nzd0165.xlsx
+++ b/data/nzd0165/nzd0165.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H389"/>
+  <dimension ref="A1:H391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12108,6 +12108,66 @@
         <v>410.52</v>
       </c>
       <c r="H389" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>434.12</v>
+      </c>
+      <c r="C390" t="n">
+        <v>411.61</v>
+      </c>
+      <c r="D390" t="n">
+        <v>410.78</v>
+      </c>
+      <c r="E390" t="n">
+        <v>404.34</v>
+      </c>
+      <c r="F390" t="n">
+        <v>400.71</v>
+      </c>
+      <c r="G390" t="n">
+        <v>410.44</v>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:05:51+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="C391" t="n">
+        <v>409.84</v>
+      </c>
+      <c r="D391" t="n">
+        <v>408.98</v>
+      </c>
+      <c r="E391" t="n">
+        <v>402.54</v>
+      </c>
+      <c r="F391" t="n">
+        <v>398.26</v>
+      </c>
+      <c r="G391" t="n">
+        <v>407.7</v>
+      </c>
+      <c r="H391" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12124,7 +12184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B414"/>
+  <dimension ref="A1:B416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16267,6 +16327,26 @@
       </c>
       <c r="B414" t="n">
         <v>-0.32</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -16435,28 +16515,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1067884324969807</v>
+        <v>0.1109395204601721</v>
       </c>
       <c r="J2" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K2" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02088288687556905</v>
+        <v>0.02268447136580554</v>
       </c>
       <c r="M2" t="n">
-        <v>4.246386726617079</v>
+        <v>4.24589538060673</v>
       </c>
       <c r="N2" t="n">
-        <v>29.07572662194866</v>
+        <v>29.01066589197821</v>
       </c>
       <c r="O2" t="n">
-        <v>5.392191263479873</v>
+        <v>5.386155019304421</v>
       </c>
       <c r="P2" t="n">
-        <v>426.8787097997621</v>
+        <v>426.8336978389083</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16513,28 +16593,28 @@
         <v>0.0638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02693066646600724</v>
+        <v>0.03017945096255793</v>
       </c>
       <c r="J3" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K3" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001800308015044494</v>
+        <v>0.002279501335511469</v>
       </c>
       <c r="M3" t="n">
-        <v>3.845584353308507</v>
+        <v>3.840094286325979</v>
       </c>
       <c r="N3" t="n">
-        <v>21.86768790293913</v>
+        <v>21.81075532870107</v>
       </c>
       <c r="O3" t="n">
-        <v>4.676289972076061</v>
+        <v>4.670198639105307</v>
       </c>
       <c r="P3" t="n">
-        <v>406.8210400004351</v>
+        <v>406.7858153977334</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16591,28 +16671,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02436546719996021</v>
+        <v>0.02688267512296326</v>
       </c>
       <c r="J4" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K4" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002055722919553804</v>
+        <v>0.002523831601458193</v>
       </c>
       <c r="M4" t="n">
-        <v>3.221067048896789</v>
+        <v>3.214668003074097</v>
       </c>
       <c r="N4" t="n">
-        <v>15.67217413574094</v>
+        <v>15.62665824234445</v>
       </c>
       <c r="O4" t="n">
-        <v>3.958809686729199</v>
+        <v>3.953056822554471</v>
       </c>
       <c r="P4" t="n">
-        <v>406.7593051664946</v>
+        <v>406.7320136903818</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16669,28 +16749,28 @@
         <v>0.0835</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.007292563197062764</v>
+        <v>-0.00856794917836619</v>
       </c>
       <c r="J5" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K5" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001811087790755117</v>
+        <v>0.0002526072638415755</v>
       </c>
       <c r="M5" t="n">
-        <v>3.102014853436293</v>
+        <v>3.092773112946416</v>
       </c>
       <c r="N5" t="n">
-        <v>15.96541773204402</v>
+        <v>15.89561009915334</v>
       </c>
       <c r="O5" t="n">
-        <v>3.995674878170647</v>
+        <v>3.986929908984273</v>
       </c>
       <c r="P5" t="n">
-        <v>404.8848110702317</v>
+        <v>404.8986457655903</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16747,28 +16827,28 @@
         <v>0.0956</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09743074638969809</v>
+        <v>-0.1000215220173215</v>
       </c>
       <c r="J6" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K6" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02920835072432704</v>
+        <v>0.03099934586157393</v>
       </c>
       <c r="M6" t="n">
-        <v>3.174444141687404</v>
+        <v>3.173562238074552</v>
       </c>
       <c r="N6" t="n">
-        <v>17.15730628462453</v>
+        <v>17.10950523105232</v>
       </c>
       <c r="O6" t="n">
-        <v>4.14213788817134</v>
+        <v>4.136363769188141</v>
       </c>
       <c r="P6" t="n">
-        <v>404.6274383398347</v>
+        <v>404.6555385048053</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16825,28 +16905,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1019312985922358</v>
+        <v>-0.1036352665341082</v>
       </c>
       <c r="J7" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K7" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03234015978468707</v>
+        <v>0.03371230794229096</v>
       </c>
       <c r="M7" t="n">
-        <v>3.379593331039628</v>
+        <v>3.370620262707969</v>
       </c>
       <c r="N7" t="n">
-        <v>16.90572181013353</v>
+        <v>16.84271470757009</v>
       </c>
       <c r="O7" t="n">
-        <v>4.111656820569237</v>
+        <v>4.103987659285793</v>
       </c>
       <c r="P7" t="n">
-        <v>413.4672299372172</v>
+        <v>413.4857144974331</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16884,7 +16964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H389"/>
+  <dimension ref="A1:H391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33225,6 +33305,90 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>-36.764380760619545,175.14465828673386</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>-36.76460925696665,175.14542467954004</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>-36.76444191720963,175.14614455273693</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-36.76418586168581,175.14688947879054</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>-36.763815024147696,175.14760999119204</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>-36.763306552477005,175.1482372333812</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:05:51+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>-36.76438634679995,175.1446581971407</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>-36.76462502120607,175.14542768785364</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>-36.76445678145037,175.1461526191208</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-36.764199481652774,175.1469004248794</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-36.76383246425711,175.14762681404844</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-36.7633256807537,175.1482566348215</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
